--- a/docs/collections/naoe/metadata/data.xlsx
+++ b/docs/collections/naoe/metadata/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,90 +449,95 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>transcription</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ウェブサイトURL</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>アイテムURL</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>サムネイル</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>機械可読ドキュメント</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>帰属</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>viewingDirection</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>viewingHint</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>コレクション</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ソート用項目</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>西暦</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>IIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>IIIF Search API URI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>アノテーション付きIIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Link to TAPAS Project</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Text with Rich Text Format</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t># of media</t>
         </is>
@@ -571,90 +576,95 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>scripto:transcription</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>bibo:identifier</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>dcterms:isPartOf</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>dcterms:relation</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>foaf:thumbnail</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>rdfs:seeAlso</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>sc:attributionLabel</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>sc:viewingDirection</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>sc:viewingHint</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>uterms:databaseLabel</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>uterms:sort</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>uterms:year</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>uterms:manifestUri</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>uterms:searchApiUri</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>uterms:annotedManifest</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>uterms:linkToTapas</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>uterms:rtf</t>
         </is>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>31</v>
       </c>
     </row>
@@ -682,74 +692,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>https://utda.github.io/tei-viewer/?v=true&amp;u=https://archdataset.dl.itc.u-tokyo.ac.jp/collections/naoe/text/xml/daaf81b0-f1a7-435c-9216-a8fb56390887.xml</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/daaf81b0-f1a7-435c-9216-a8fb56390887.json</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>daaf81b0-f1a7-435c-9216-a8fb56390887</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/naoe/</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/naoe/document/daaf81b0-f1a7-435c-9216-a8fb56390887</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/bd56abac4d291f381b7cf64e6fa3b9b6bc59b44b.jpg</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/13</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>東京大学総合図書館 General Library in the University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>直江状</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/daaf81b0-f1a7-435c-9216-a8fb56390887/manifest</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>https://w3id.org/dhj/i3sa/https://archdataset.dl.itc.u-tokyo.ac.jp/collections/naoe/text/xml/daaf81b0-f1a7-435c-9216-a8fb56390887.xml</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/omekac/oa/collections/8/manifest.json</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>http://tapasproject.org/tapas-commons/files/直江状</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="n">
         <v>31</v>
       </c>
     </row>
